--- a/analysis/results/statistical_analysis.xlsx
+++ b/analysis/results/statistical_analysis.xlsx
@@ -582,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed_no_quantum</t>
         </is>
       </c>
       <c r="D34" t="n">
